--- a/SGC-CKN/Excel/bb1fd7cb-f10d-4d9a-8fae-653a9ceac55d_Thanh_Hoá_P-160_D800_30-03-2026.xlsx
+++ b/SGC-CKN/Excel/bb1fd7cb-f10d-4d9a-8fae-653a9ceac55d_Thanh_Hoá_P-160_D800_30-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="63">
   <si>
     <t>Dự án</t>
   </si>
@@ -116,35 +116,27 @@
 21/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">00:00
-22/03/2026</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Cát pha xám ghi, xám nâu TT dẻo</t>
-  </si>
-  <si>
     <t xml:space="preserve">22:00
 22/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">00:00
-23/03/2026</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>Sét xám trắng, xám xanh dẻo chảy</t>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Cát pha xám ghi, xám nâu TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">23:01
 23/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">05:55
+    <t>4</t>
+  </si>
+  <si>
+    <t>Sét xám trắng, xám xanh dẻo chảy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:55
 30/03/2026</t>
   </si>
   <si>
@@ -154,7 +146,7 @@
     <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
   </si>
   <si>
-    <t xml:space="preserve">11:57
+    <t xml:space="preserve">1:57
 30/03/2026</t>
   </si>
   <si>
@@ -164,7 +156,7 @@
     <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
-    <t xml:space="preserve">12:40
+    <t xml:space="preserve">2:40
 30/03/2026</t>
   </si>
   <si>
@@ -174,7 +166,7 @@
     <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">13:40
+    <t xml:space="preserve">3:40
 30/03/2026</t>
   </si>
   <si>
@@ -184,8 +176,11 @@
     <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">15:30
+    <t xml:space="preserve">5:30
 30/03/2026</t>
+  </si>
+  <si>
+    <t>NT chạm sỏi CĐ: 38,9</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>
@@ -263,6 +258,12 @@
       <name val="Arial"/>
     </font>
     <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <color rgb="FF065F46"/>
       <sz val="10"/>
       <name val="Arial"/>
@@ -274,12 +275,6 @@
     </font>
     <font>
       <color rgb="FF4C1D95"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
@@ -350,6 +345,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDC2626"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA7F3D0"/>
       </patternFill>
     </fill>
@@ -365,7 +365,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC2626"/>
+        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
@@ -376,11 +376,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFED7AA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
@@ -519,12 +514,6 @@
     <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -546,26 +535,32 @@
     <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1209,231 +1204,231 @@
         <v>-4.8</v>
       </c>
       <c r="H12" s="9">
-        <v>2.92</v>
+        <v>24.92</v>
       </c>
       <c r="I12" s="9">
         <v>3.2</v>
       </c>
-      <c r="J12" s="8">
-        <v>1.1</v>
+      <c r="J12" s="12">
+        <v>0.13</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="F13" s="13">
+        <v>-4.8</v>
+      </c>
+      <c r="G13" s="13">
+        <v>-8.1</v>
+      </c>
+      <c r="H13" s="13">
+        <v>25.02</v>
+      </c>
+      <c r="I13" s="13">
+        <v>3.3</v>
+      </c>
+      <c r="J13" s="12">
+        <v>0.13</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="F13" s="12">
-        <v>-4.8</v>
-      </c>
-      <c r="G13" s="12">
+      <c r="B14" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="16">
         <v>-8.1</v>
       </c>
-      <c r="H13" s="12">
-        <v>2</v>
-      </c>
-      <c r="I13" s="12">
-        <v>3.3</v>
-      </c>
-      <c r="J13" s="8">
-        <v>1.65</v>
-      </c>
-      <c r="K13" s="13" t="s">
+      <c r="G14" s="16">
+        <v>-16.8</v>
+      </c>
+      <c r="H14" s="16">
+        <v>145.9</v>
+      </c>
+      <c r="I14" s="16">
+        <v>8.7</v>
+      </c>
+      <c r="J14" s="12">
+        <v>0.06</v>
+      </c>
+      <c r="K14" s="17" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="15" t="s">
+    <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C15" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="F14" s="15">
-        <v>-8.1</v>
-      </c>
-      <c r="G14" s="15">
+      <c r="E15" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" s="19">
         <v>-16.8</v>
       </c>
-      <c r="H14" s="15">
-        <v>6.9</v>
-      </c>
-      <c r="I14" s="15">
-        <v>8.7</v>
-      </c>
-      <c r="J14" s="8">
-        <v>1.26</v>
-      </c>
-      <c r="K14" s="16" t="s">
+      <c r="G15" s="19">
+        <v>-22.5</v>
+      </c>
+      <c r="H15" s="19">
+        <v>1.03</v>
+      </c>
+      <c r="I15" s="19">
+        <v>5.7</v>
+      </c>
+      <c r="J15" s="22">
+        <v>5.52</v>
+      </c>
+      <c r="K15" s="20" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
+    <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="E15" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="F15" s="18">
-        <v>-16.8</v>
-      </c>
-      <c r="G15" s="18">
+      <c r="E16" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="F16" s="23">
         <v>-22.5</v>
       </c>
-      <c r="H15" s="18">
-        <v>6.03</v>
-      </c>
-      <c r="I15" s="18">
-        <v>5.7</v>
-      </c>
-      <c r="J15" s="21">
-        <v>0.94</v>
-      </c>
-      <c r="K15" s="19" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="B16" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="F16" s="22">
-        <v>-22.5</v>
-      </c>
-      <c r="G16" s="22">
+      <c r="G16" s="23">
         <v>-25.7</v>
       </c>
-      <c r="H16" s="22">
+      <c r="H16" s="23">
         <v>0.72</v>
       </c>
-      <c r="I16" s="22">
+      <c r="I16" s="23">
         <v>3.2</v>
       </c>
       <c r="J16" s="8">
         <v>4.47</v>
       </c>
-      <c r="K16" s="23" t="s">
+      <c r="K16" s="24" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="D17" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="E17" s="27" t="s">
-        <v>50</v>
-      </c>
-      <c r="F17" s="25">
+      <c r="F17" s="26">
         <v>-25.7</v>
       </c>
-      <c r="G17" s="25">
+      <c r="G17" s="26">
         <v>-35.4</v>
       </c>
-      <c r="H17" s="25">
+      <c r="H17" s="26">
         <v>1</v>
       </c>
-      <c r="I17" s="25">
+      <c r="I17" s="26">
         <v>9.7</v>
       </c>
-      <c r="J17" s="28">
+      <c r="J17" s="22">
         <v>9.7</v>
       </c>
-      <c r="K17" s="26" t="s">
+      <c r="K17" s="27" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="29" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B18" s="29" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="30" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D18" s="31" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E18" s="31" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F18" s="29">
         <v>-35.4</v>
       </c>
       <c r="G18" s="29">
-        <v>-47</v>
+        <v>-44</v>
       </c>
       <c r="H18" s="29">
         <v>1.83</v>
       </c>
       <c r="I18" s="29">
-        <v>11.6</v>
-      </c>
-      <c r="J18" s="28">
-        <v>6.33</v>
+        <v>8.6</v>
+      </c>
+      <c r="J18" s="8">
+        <v>4.69</v>
       </c>
       <c r="K18" s="30" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="32" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B21" s="32"/>
       <c r="C21" s="32"/>
@@ -1539,31 +1534,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1615,125 +1610,125 @@
         <v>-4.8</v>
       </c>
       <c r="G3" s="9">
-        <v>2.92</v>
+        <v>24.92</v>
       </c>
       <c r="H3" s="9">
         <v>3.2</v>
       </c>
-      <c r="I3" s="8">
-        <v>1.1</v>
+      <c r="I3" s="12">
+        <v>0.13</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="12">
+      <c r="A4" s="13">
         <v>3</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="13">
         <v>1</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="13">
         <v>-4.8</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="13">
         <v>-8.1</v>
       </c>
-      <c r="G4" s="12">
-        <v>2</v>
-      </c>
-      <c r="H4" s="12">
+      <c r="G4" s="13">
+        <v>25.02</v>
+      </c>
+      <c r="H4" s="13">
         <v>3.3</v>
       </c>
-      <c r="I4" s="8">
-        <v>1.65</v>
+      <c r="I4" s="12">
+        <v>0.13</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="15">
+      <c r="A5" s="16">
         <v>4</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" s="15">
+      <c r="C5" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="16">
         <v>1</v>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="16">
         <v>-8.1</v>
       </c>
-      <c r="F5" s="15">
+      <c r="F5" s="16">
         <v>-16.8</v>
       </c>
-      <c r="G5" s="15">
-        <v>6.9</v>
-      </c>
-      <c r="H5" s="15">
+      <c r="G5" s="16">
+        <v>145.9</v>
+      </c>
+      <c r="H5" s="16">
         <v>8.7</v>
       </c>
-      <c r="I5" s="8">
-        <v>1.26</v>
+      <c r="I5" s="12">
+        <v>0.06</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="18">
+      <c r="A6" s="19">
         <v>5</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="D6" s="18">
+      <c r="C6" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="19">
         <v>1</v>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="19">
         <v>-16.8</v>
       </c>
-      <c r="F6" s="18">
+      <c r="F6" s="19">
         <v>-22.5</v>
       </c>
-      <c r="G6" s="18">
-        <v>6.03</v>
-      </c>
-      <c r="H6" s="18">
+      <c r="G6" s="19">
+        <v>1.03</v>
+      </c>
+      <c r="H6" s="19">
         <v>5.7</v>
       </c>
-      <c r="I6" s="21">
-        <v>0.94</v>
+      <c r="I6" s="22">
+        <v>5.52</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="22">
+      <c r="A7" s="23">
         <v>6</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="D7" s="22">
+      <c r="C7" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="23">
         <v>1</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="23">
         <v>-22.5</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="23">
         <v>-25.7</v>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="23">
         <v>0.72</v>
       </c>
-      <c r="H7" s="22">
+      <c r="H7" s="23">
         <v>3.2</v>
       </c>
       <c r="I7" s="8">
@@ -1741,31 +1736,31 @@
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="25">
+      <c r="A8" s="26">
         <v>7</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="D8" s="25">
+      <c r="C8" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="26">
         <v>1</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="26">
         <v>-25.7</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="26">
         <v>-35.4</v>
       </c>
-      <c r="G8" s="25">
+      <c r="G8" s="26">
         <v>1</v>
       </c>
-      <c r="H8" s="25">
+      <c r="H8" s="26">
         <v>9.7</v>
       </c>
-      <c r="I8" s="28">
+      <c r="I8" s="22">
         <v>9.7</v>
       </c>
     </row>
@@ -1777,7 +1772,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="30" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D9" s="29">
         <v>1</v>
@@ -1786,21 +1781,21 @@
         <v>-35.4</v>
       </c>
       <c r="F9" s="29">
-        <v>-47</v>
+        <v>-44</v>
       </c>
       <c r="G9" s="29">
         <v>1.83</v>
       </c>
       <c r="H9" s="29">
-        <v>11.6</v>
-      </c>
-      <c r="I9" s="28">
-        <v>6.33</v>
+        <v>8.6</v>
+      </c>
+      <c r="I9" s="8">
+        <v>4.69</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="33" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B10" s="34" t="s">
         <v>29</v>
@@ -1815,16 +1810,16 @@
         <v>0</v>
       </c>
       <c r="F10" s="34">
-        <v>-47</v>
+        <v>-44</v>
       </c>
       <c r="G10" s="34">
-        <v>22.48</v>
+        <v>201.5</v>
       </c>
       <c r="H10" s="34">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="I10" s="34">
-        <v>2.09</v>
+        <v>0.22</v>
       </c>
     </row>
   </sheetData>

--- a/SGC-CKN/Excel/bb1fd7cb-f10d-4d9a-8fae-653a9ceac55d_Thanh_Hoá_P-160_D800_30-03-2026.xlsx
+++ b/SGC-CKN/Excel/bb1fd7cb-f10d-4d9a-8fae-653a9ceac55d_Thanh_Hoá_P-160_D800_30-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="64">
   <si>
     <t>Dự án</t>
   </si>
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>P-160</t>
+    <t>P1-160</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>
@@ -116,27 +116,35 @@
 21/03/2026</t>
   </si>
   <si>
+    <t xml:space="preserve">00:00
+22/03/2026</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Cát pha xám ghi, xám nâu TT dẻo</t>
+  </si>
+  <si>
     <t xml:space="preserve">22:00
 22/03/2026</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Cát pha xám ghi, xám nâu TT dẻo</t>
+    <t xml:space="preserve">00:00
+23/03/2026</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Sét xám trắng, xám xanh dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">23:01
 23/03/2026</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>Sét xám trắng, xám xanh dẻo chảy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:55
+    <t xml:space="preserve">05:55
 30/03/2026</t>
   </si>
   <si>
@@ -146,7 +154,7 @@
     <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
   </si>
   <si>
-    <t xml:space="preserve">1:57
+    <t xml:space="preserve">11:57
 30/03/2026</t>
   </si>
   <si>
@@ -156,7 +164,7 @@
     <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
-    <t xml:space="preserve">2:40
+    <t xml:space="preserve">12:40
 30/03/2026</t>
   </si>
   <si>
@@ -166,7 +174,7 @@
     <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">3:40
+    <t xml:space="preserve">13:40
 30/03/2026</t>
   </si>
   <si>
@@ -176,11 +184,8 @@
     <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">5:30
+    <t xml:space="preserve">15:30
 30/03/2026</t>
-  </si>
-  <si>
-    <t>NT chạm sỏi CĐ: 38,9</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>
@@ -258,12 +263,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <color rgb="FF065F46"/>
       <sz val="10"/>
       <name val="Arial"/>
@@ -275,6 +274,12 @@
     </font>
     <font>
       <color rgb="FF4C1D95"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
@@ -345,11 +350,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC2626"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA7F3D0"/>
       </patternFill>
     </fill>
@@ -365,7 +365,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
+        <fgColor rgb="FFDC2626"/>
       </patternFill>
     </fill>
     <fill>
@@ -376,6 +376,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFED7AA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
@@ -514,6 +519,12 @@
     <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -535,32 +546,26 @@
     <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1204,231 +1209,231 @@
         <v>-4.8</v>
       </c>
       <c r="H12" s="9">
-        <v>24.92</v>
+        <v>2.92</v>
       </c>
       <c r="I12" s="9">
         <v>3.2</v>
       </c>
-      <c r="J12" s="12">
-        <v>0.13</v>
+      <c r="J12" s="8">
+        <v>1.1</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="E13" s="15" t="s">
+      <c r="D13" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="F13" s="13">
+      <c r="E13" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" s="12">
         <v>-4.8</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="12">
         <v>-8.1</v>
       </c>
-      <c r="H13" s="13">
-        <v>25.02</v>
-      </c>
-      <c r="I13" s="13">
+      <c r="H13" s="12">
+        <v>2</v>
+      </c>
+      <c r="I13" s="12">
         <v>3.3</v>
       </c>
-      <c r="J13" s="12">
-        <v>0.13</v>
-      </c>
-      <c r="K13" s="14" t="s">
+      <c r="J13" s="8">
+        <v>1.65</v>
+      </c>
+      <c r="K13" s="13" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" s="16" t="s">
+      <c r="A14" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="E14" s="18" t="s">
+      <c r="C14" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="F14" s="16">
+      <c r="D14" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="F14" s="15">
         <v>-8.1</v>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="15">
         <v>-16.8</v>
       </c>
-      <c r="H14" s="16">
-        <v>145.9</v>
-      </c>
-      <c r="I14" s="16">
+      <c r="H14" s="15">
+        <v>6.9</v>
+      </c>
+      <c r="I14" s="15">
         <v>8.7</v>
       </c>
-      <c r="J14" s="12">
-        <v>0.06</v>
-      </c>
-      <c r="K14" s="17" t="s">
+      <c r="J14" s="8">
+        <v>1.26</v>
+      </c>
+      <c r="K14" s="16" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="B15" s="19" t="s">
+      <c r="A15" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="E15" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="F15" s="19">
+      <c r="E15" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="F15" s="18">
         <v>-16.8</v>
       </c>
-      <c r="G15" s="19">
+      <c r="G15" s="18">
         <v>-22.5</v>
       </c>
-      <c r="H15" s="19">
-        <v>1.03</v>
-      </c>
-      <c r="I15" s="19">
+      <c r="H15" s="18">
+        <v>6.03</v>
+      </c>
+      <c r="I15" s="18">
         <v>5.7</v>
       </c>
-      <c r="J15" s="22">
-        <v>5.52</v>
-      </c>
-      <c r="K15" s="20" t="s">
+      <c r="J15" s="21">
+        <v>0.94</v>
+      </c>
+      <c r="K15" s="19" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="23" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" s="23" t="s">
+      <c r="A16" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="24" t="s">
+      <c r="C16" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="E16" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="F16" s="23">
+      <c r="E16" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16" s="22">
         <v>-22.5</v>
       </c>
-      <c r="G16" s="23">
+      <c r="G16" s="22">
         <v>-25.7</v>
       </c>
-      <c r="H16" s="23">
+      <c r="H16" s="22">
         <v>0.72</v>
       </c>
-      <c r="I16" s="23">
+      <c r="I16" s="22">
         <v>3.2</v>
       </c>
       <c r="J16" s="8">
         <v>4.47</v>
       </c>
-      <c r="K16" s="24" t="s">
+      <c r="K16" s="23" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="B17" s="26" t="s">
+      <c r="A17" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="27" t="s">
+      <c r="C17" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="D17" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="E17" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="F17" s="26">
+      <c r="E17" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="F17" s="25">
         <v>-25.7</v>
       </c>
-      <c r="G17" s="26">
+      <c r="G17" s="25">
         <v>-35.4</v>
       </c>
-      <c r="H17" s="26">
+      <c r="H17" s="25">
         <v>1</v>
       </c>
-      <c r="I17" s="26">
+      <c r="I17" s="25">
         <v>9.7</v>
       </c>
-      <c r="J17" s="22">
+      <c r="J17" s="28">
         <v>9.7</v>
       </c>
-      <c r="K17" s="27" t="s">
+      <c r="K17" s="26" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="29" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B18" s="29" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="31" t="s">
-        <v>48</v>
-      </c>
       <c r="E18" s="31" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F18" s="29">
         <v>-35.4</v>
       </c>
       <c r="G18" s="29">
-        <v>-44</v>
+        <v>-47</v>
       </c>
       <c r="H18" s="29">
         <v>1.83</v>
       </c>
       <c r="I18" s="29">
-        <v>8.6</v>
-      </c>
-      <c r="J18" s="8">
-        <v>4.69</v>
+        <v>11.6</v>
+      </c>
+      <c r="J18" s="28">
+        <v>6.33</v>
       </c>
       <c r="K18" s="30" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B21" s="32"/>
       <c r="C21" s="32"/>
@@ -1534,31 +1539,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1610,125 +1615,125 @@
         <v>-4.8</v>
       </c>
       <c r="G3" s="9">
-        <v>24.92</v>
+        <v>2.92</v>
       </c>
       <c r="H3" s="9">
         <v>3.2</v>
       </c>
-      <c r="I3" s="12">
-        <v>0.13</v>
+      <c r="I3" s="8">
+        <v>1.1</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="13">
+      <c r="A4" s="12">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="12">
         <v>1</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="12">
         <v>-4.8</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="12">
         <v>-8.1</v>
       </c>
-      <c r="G4" s="13">
-        <v>25.02</v>
-      </c>
-      <c r="H4" s="13">
+      <c r="G4" s="12">
+        <v>2</v>
+      </c>
+      <c r="H4" s="12">
         <v>3.3</v>
       </c>
-      <c r="I4" s="12">
-        <v>0.13</v>
+      <c r="I4" s="8">
+        <v>1.65</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="16">
+      <c r="A5" s="15">
         <v>4</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" s="16">
+      <c r="C5" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="15">
         <v>1</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="15">
         <v>-8.1</v>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="15">
         <v>-16.8</v>
       </c>
-      <c r="G5" s="16">
-        <v>145.9</v>
-      </c>
-      <c r="H5" s="16">
+      <c r="G5" s="15">
+        <v>6.9</v>
+      </c>
+      <c r="H5" s="15">
         <v>8.7</v>
       </c>
-      <c r="I5" s="12">
-        <v>0.06</v>
+      <c r="I5" s="8">
+        <v>1.26</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="19">
+      <c r="A6" s="18">
         <v>5</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" s="19">
+      <c r="C6" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="18">
         <v>1</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="18">
         <v>-16.8</v>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="18">
         <v>-22.5</v>
       </c>
-      <c r="G6" s="19">
-        <v>1.03</v>
-      </c>
-      <c r="H6" s="19">
+      <c r="G6" s="18">
+        <v>6.03</v>
+      </c>
+      <c r="H6" s="18">
         <v>5.7</v>
       </c>
-      <c r="I6" s="22">
-        <v>5.52</v>
+      <c r="I6" s="21">
+        <v>0.94</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="23">
+      <c r="A7" s="22">
         <v>6</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="D7" s="23">
+      <c r="C7" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" s="22">
         <v>1</v>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="22">
         <v>-22.5</v>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="22">
         <v>-25.7</v>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="22">
         <v>0.72</v>
       </c>
-      <c r="H7" s="23">
+      <c r="H7" s="22">
         <v>3.2</v>
       </c>
       <c r="I7" s="8">
@@ -1736,31 +1741,31 @@
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="26">
+      <c r="A8" s="25">
         <v>7</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" s="26">
+      <c r="C8" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="25">
         <v>1</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="25">
         <v>-25.7</v>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="25">
         <v>-35.4</v>
       </c>
-      <c r="G8" s="26">
+      <c r="G8" s="25">
         <v>1</v>
       </c>
-      <c r="H8" s="26">
+      <c r="H8" s="25">
         <v>9.7</v>
       </c>
-      <c r="I8" s="22">
+      <c r="I8" s="28">
         <v>9.7</v>
       </c>
     </row>
@@ -1772,7 +1777,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="30" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D9" s="29">
         <v>1</v>
@@ -1781,21 +1786,21 @@
         <v>-35.4</v>
       </c>
       <c r="F9" s="29">
-        <v>-44</v>
+        <v>-47</v>
       </c>
       <c r="G9" s="29">
         <v>1.83</v>
       </c>
       <c r="H9" s="29">
-        <v>8.6</v>
-      </c>
-      <c r="I9" s="8">
-        <v>4.69</v>
+        <v>11.6</v>
+      </c>
+      <c r="I9" s="28">
+        <v>6.33</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="33" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B10" s="34" t="s">
         <v>29</v>
@@ -1810,16 +1815,16 @@
         <v>0</v>
       </c>
       <c r="F10" s="34">
-        <v>-44</v>
+        <v>-47</v>
       </c>
       <c r="G10" s="34">
-        <v>201.5</v>
+        <v>22.48</v>
       </c>
       <c r="H10" s="34">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="I10" s="34">
-        <v>0.22</v>
+        <v>2.09</v>
       </c>
     </row>
   </sheetData>

--- a/SGC-CKN/Excel/bb1fd7cb-f10d-4d9a-8fae-653a9ceac55d_Thanh_Hoá_P-160_D800_30-03-2026.xlsx
+++ b/SGC-CKN/Excel/bb1fd7cb-f10d-4d9a-8fae-653a9ceac55d_Thanh_Hoá_P-160_D800_30-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="62">
   <si>
     <t>Dự án</t>
   </si>
@@ -53,7 +53,7 @@
     <t>Bắt đầu thi công</t>
   </si>
   <si>
-    <t>20:00 19/03/2026</t>
+    <t>20:00 29/03/2026</t>
   </si>
   <si>
     <t>Kết thúc thi công</t>
@@ -96,11 +96,11 @@
   </si>
   <si>
     <t xml:space="preserve">20:00
-19/03/2026</t>
+29/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">21:05
-19/03/2026</t>
+29/03/2026</t>
   </si>
   <si>
     <t/>
@@ -112,12 +112,8 @@
     <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
   </si>
   <si>
-    <t xml:space="preserve">21:05
-21/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">00:00
-22/03/2026</t>
+    <t xml:space="preserve">22:00
+29/03/2026</t>
   </si>
   <si>
     <t>3</t>
@@ -126,12 +122,8 @@
     <t>Cát pha xám ghi, xám nâu TT dẻo</t>
   </si>
   <si>
-    <t xml:space="preserve">22:00
-22/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">00:00
-23/03/2026</t>
+    <t xml:space="preserve">23:00
+29/03/2026</t>
   </si>
   <si>
     <t>4</t>
@@ -141,11 +133,11 @@
   </si>
   <si>
     <t xml:space="preserve">23:01
-23/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05:55
-30/03/2026</t>
+29/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:55
+29/03/2026</t>
   </si>
   <si>
     <t>5</t>
@@ -154,8 +146,8 @@
     <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
   </si>
   <si>
-    <t xml:space="preserve">11:57
-30/03/2026</t>
+    <t xml:space="preserve">1:57
+29/03/2026</t>
   </si>
   <si>
     <t>6</t>
@@ -164,8 +156,8 @@
     <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
-    <t xml:space="preserve">12:40
-30/03/2026</t>
+    <t xml:space="preserve">2:40
+29/03/2026</t>
   </si>
   <si>
     <t>7</t>
@@ -174,8 +166,8 @@
     <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">13:40
-30/03/2026</t>
+    <t xml:space="preserve">3:40
+29/03/2026</t>
   </si>
   <si>
     <t>8</t>
@@ -184,8 +176,8 @@
     <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">15:30
-30/03/2026</t>
+    <t xml:space="preserve">5:30
+29/03/2026</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>
@@ -222,7 +214,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -278,12 +270,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <color rgb="FF365314"/>
       <sz val="10"/>
       <name val="Arial"/>
@@ -311,7 +297,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -365,7 +351,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC2626"/>
+        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
@@ -376,11 +362,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFED7AA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
@@ -481,7 +462,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -543,46 +524,43 @@
     <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1197,10 +1175,10 @@
         <v>31</v>
       </c>
       <c r="D12" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="11" t="s">
         <v>32</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>33</v>
       </c>
       <c r="F12" s="9">
         <v>-1.6</v>
@@ -1209,13 +1187,13 @@
         <v>-4.8</v>
       </c>
       <c r="H12" s="9">
-        <v>2.92</v>
+        <v>0.92</v>
       </c>
       <c r="I12" s="9">
         <v>3.2</v>
       </c>
       <c r="J12" s="8">
-        <v>1.1</v>
+        <v>3.49</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>29</v>
@@ -1223,19 +1201,19 @@
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" s="14" t="s">
         <v>35</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>37</v>
       </c>
       <c r="F13" s="12">
         <v>-4.8</v>
@@ -1244,13 +1222,13 @@
         <v>-8.1</v>
       </c>
       <c r="H13" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I13" s="12">
         <v>3.3</v>
       </c>
       <c r="J13" s="8">
-        <v>1.65</v>
+        <v>3.3</v>
       </c>
       <c r="K13" s="13" t="s">
         <v>29</v>
@@ -1258,19 +1236,19 @@
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="17" t="s">
         <v>39</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>41</v>
       </c>
       <c r="F14" s="15">
         <v>-8.1</v>
@@ -1279,13 +1257,13 @@
         <v>-16.8</v>
       </c>
       <c r="H14" s="15">
-        <v>6.9</v>
+        <v>1.9</v>
       </c>
       <c r="I14" s="15">
         <v>8.7</v>
       </c>
       <c r="J14" s="8">
-        <v>1.26</v>
+        <v>4.58</v>
       </c>
       <c r="K14" s="16" t="s">
         <v>29</v>
@@ -1293,19 +1271,19 @@
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B15" s="18" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F15" s="18">
         <v>-16.8</v>
@@ -1314,13 +1292,13 @@
         <v>-22.5</v>
       </c>
       <c r="H15" s="18">
-        <v>6.03</v>
+        <v>1.03</v>
       </c>
       <c r="I15" s="18">
         <v>5.7</v>
       </c>
       <c r="J15" s="21">
-        <v>0.94</v>
+        <v>5.52</v>
       </c>
       <c r="K15" s="19" t="s">
         <v>29</v>
@@ -1328,19 +1306,19 @@
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B16" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F16" s="22">
         <v>-22.5</v>
@@ -1363,19 +1341,19 @@
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B17" s="25" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F17" s="25">
         <v>-25.7</v>
@@ -1389,7 +1367,7 @@
       <c r="I17" s="25">
         <v>9.7</v>
       </c>
-      <c r="J17" s="28">
+      <c r="J17" s="21">
         <v>9.7</v>
       </c>
       <c r="K17" s="26" t="s">
@@ -1397,54 +1375,54 @@
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" s="30" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="30" t="s">
+      <c r="F18" s="28">
+        <v>-35.4</v>
+      </c>
+      <c r="G18" s="28">
+        <v>-47</v>
+      </c>
+      <c r="H18" s="28">
+        <v>1.83</v>
+      </c>
+      <c r="I18" s="28">
+        <v>11.6</v>
+      </c>
+      <c r="J18" s="21">
+        <v>6.33</v>
+      </c>
+      <c r="K18" s="29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="D18" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="E18" s="31" t="s">
-        <v>53</v>
-      </c>
-      <c r="F18" s="29">
-        <v>-35.4</v>
-      </c>
-      <c r="G18" s="29">
-        <v>-47</v>
-      </c>
-      <c r="H18" s="29">
-        <v>1.83</v>
-      </c>
-      <c r="I18" s="29">
-        <v>11.6</v>
-      </c>
-      <c r="J18" s="28">
-        <v>6.33</v>
-      </c>
-      <c r="K18" s="30" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="B21" s="32"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="32"/>
-      <c r="K21" s="32"/>
+      <c r="B21" s="31"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
     </row>
     <row r="22" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1539,31 +1517,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1615,13 +1593,13 @@
         <v>-4.8</v>
       </c>
       <c r="G3" s="9">
-        <v>2.92</v>
+        <v>0.92</v>
       </c>
       <c r="H3" s="9">
         <v>3.2</v>
       </c>
       <c r="I3" s="8">
-        <v>1.1</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1632,7 +1610,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4" s="12">
         <v>1</v>
@@ -1644,13 +1622,13 @@
         <v>-8.1</v>
       </c>
       <c r="G4" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" s="12">
         <v>3.3</v>
       </c>
       <c r="I4" s="8">
-        <v>1.65</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1661,7 +1639,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D5" s="15">
         <v>1</v>
@@ -1673,13 +1651,13 @@
         <v>-16.8</v>
       </c>
       <c r="G5" s="15">
-        <v>6.9</v>
+        <v>1.9</v>
       </c>
       <c r="H5" s="15">
         <v>8.7</v>
       </c>
       <c r="I5" s="8">
-        <v>1.26</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1690,7 +1668,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D6" s="18">
         <v>1</v>
@@ -1702,13 +1680,13 @@
         <v>-22.5</v>
       </c>
       <c r="G6" s="18">
-        <v>6.03</v>
+        <v>1.03</v>
       </c>
       <c r="H6" s="18">
         <v>5.7</v>
       </c>
       <c r="I6" s="21">
-        <v>0.94</v>
+        <v>5.52</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1719,7 +1697,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D7" s="22">
         <v>1</v>
@@ -1748,7 +1726,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
@@ -1765,66 +1743,66 @@
       <c r="H8" s="25">
         <v>9.7</v>
       </c>
-      <c r="I8" s="28">
+      <c r="I8" s="21">
         <v>9.7</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="29">
+      <c r="A9" s="28">
         <v>8</v>
       </c>
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="30" t="s">
-        <v>52</v>
-      </c>
-      <c r="D9" s="29">
+      <c r="C9" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="28">
         <v>1</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="28">
         <v>-35.4</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="28">
         <v>-47</v>
       </c>
-      <c r="G9" s="29">
+      <c r="G9" s="28">
         <v>1.83</v>
       </c>
-      <c r="H9" s="29">
+      <c r="H9" s="28">
         <v>11.6</v>
       </c>
-      <c r="I9" s="28">
+      <c r="I9" s="21">
         <v>6.33</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="33" t="s">
-        <v>63</v>
-      </c>
-      <c r="B10" s="34" t="s">
+      <c r="A10" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="C10" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="34">
+      <c r="D10" s="33">
         <v>8</v>
       </c>
-      <c r="E10" s="34">
+      <c r="E10" s="33">
         <v>0</v>
       </c>
-      <c r="F10" s="34">
+      <c r="F10" s="33">
         <v>-47</v>
       </c>
-      <c r="G10" s="34">
-        <v>22.48</v>
-      </c>
-      <c r="H10" s="34">
+      <c r="G10" s="33">
+        <v>9.48</v>
+      </c>
+      <c r="H10" s="33">
         <v>47</v>
       </c>
-      <c r="I10" s="34">
-        <v>2.09</v>
+      <c r="I10" s="33">
+        <v>4.96</v>
       </c>
     </row>
   </sheetData>

--- a/SGC-CKN/Excel/bb1fd7cb-f10d-4d9a-8fae-653a9ceac55d_Thanh_Hoá_P-160_D800_30-03-2026.xlsx
+++ b/SGC-CKN/Excel/bb1fd7cb-f10d-4d9a-8fae-653a9ceac55d_Thanh_Hoá_P-160_D800_30-03-2026.xlsx
@@ -1394,16 +1394,16 @@
         <v>-35.4</v>
       </c>
       <c r="G18" s="28">
-        <v>-47</v>
+        <v>-44.06</v>
       </c>
       <c r="H18" s="28">
         <v>1.83</v>
       </c>
       <c r="I18" s="28">
-        <v>11.6</v>
-      </c>
-      <c r="J18" s="21">
-        <v>6.33</v>
+        <v>8.66</v>
+      </c>
+      <c r="J18" s="8">
+        <v>4.72</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>29</v>
@@ -1764,16 +1764,16 @@
         <v>-35.4</v>
       </c>
       <c r="F9" s="28">
-        <v>-47</v>
+        <v>-44.06</v>
       </c>
       <c r="G9" s="28">
         <v>1.83</v>
       </c>
       <c r="H9" s="28">
-        <v>11.6</v>
-      </c>
-      <c r="I9" s="21">
-        <v>6.33</v>
+        <v>8.66</v>
+      </c>
+      <c r="I9" s="8">
+        <v>4.72</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1793,16 +1793,16 @@
         <v>0</v>
       </c>
       <c r="F10" s="33">
-        <v>-47</v>
+        <v>-44.06</v>
       </c>
       <c r="G10" s="33">
         <v>9.48</v>
       </c>
       <c r="H10" s="33">
-        <v>47</v>
+        <v>44.06</v>
       </c>
       <c r="I10" s="33">
-        <v>4.96</v>
+        <v>4.65</v>
       </c>
     </row>
   </sheetData>
